--- a/docs/Deep Dive/09. Pipeline Control Table - What columns to keep.xlsx
+++ b/docs/Deep Dive/09. Pipeline Control Table - What columns to keep.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Data Engineering PREP\Portfolio and Profiles Improvement\FlagShip Project - retail_supply_chain_lakehouse\docs\Deep Dive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8904B1A-9BDE-4934-8EB3-395F7E97E121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984C0728-01B6-48C2-A912-1F54780BB617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{745AC0A2-2EA9-4813-A700-173DA88C4628}"/>
+    <workbookView xWindow="1536" yWindow="1236" windowWidth="21600" windowHeight="11100" xr2:uid="{745AC0A2-2EA9-4813-A700-173DA88C4628}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Table Schema" sheetId="2" r:id="rId1"/>
@@ -626,7 +626,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF9999"/>
+        <fgColor rgb="FFFCB8AA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -675,9 +675,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -687,10 +684,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1043,217 +1043,217 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="57.6" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28.8">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="28.8">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="43.2">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="11" t="b">
+      <c r="C10" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="28.8">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="11" t="b">
+      <c r="C11" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="11" t="b">
+      <c r="C12" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="11" t="b">
+      <c r="C13" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="11" t="b">
+      <c r="C14" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="28.8">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1262,6 +1262,7 @@
     <mergeCell ref="G2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
